--- a/member_deposit/2026-09-09_会员沉淀分析.xlsx
+++ b/member_deposit/2026-09-09_会员沉淀分析.xlsx
@@ -511,14 +511,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19738</v>
+        <v>19739</v>
       </c>
       <c r="C5" t="n">
-        <v>19738</v>
+        <v>19739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+19580</t>
+          <t>+19581</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87400</v>
+        <v>87401</v>
       </c>
       <c r="C8" t="n">
-        <v>87368</v>
+        <v>87369</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
